--- a/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte. Maman dit : on reste assis, avec l'adulte. Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis. Maman dit : maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture. Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
+          <t>Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte. On reste assis, avec l'adulte. Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis. Maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture. Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte.
+maman|On reste assis, avec l'adulte.
+narrateur|Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis.
+maman|Maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture.
+narrateur|Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Pierre est dans le train. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Pierre est resté assis. Dans le train, puis dans la voiture. Maman, l'adulte, était à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|La voiture s'arrête. Pierre donne la main à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Pierre est dans le train. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Pierre est resté assis. Dans le train, puis dans la voiture. Maman, l'adulte, était à côté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|La voiture s'arrête. Pierre donne la main à maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pierre reste assis dans le train</t>
+          <t>Le tunnel de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut voir la lumière après le tunnel. Le wagon s'assombrit. Elle reste assise, près de maman. Les champs reviennent.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte. On reste assis, avec l'adulte. Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis. Maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture. Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
+          <t>La lampe du wagon fait un rond jaune. Le rond tremble un peu sur les genoux. Un carré de chocolat sent le cacao. Le tissu du siège est rêche et bleu. Chouchou vit ici, avec maman. Tu as vu le rond jaune, Chouchou ? Il danse. Oui. Le train va entrer dans un tunnel. En ce moment, Chouchou s'assoit. Maman s'assoit à côté. Le dos de Chouchou touche le dossier. On reste assis, avec l'adulte. D'accord. Le train roule. Les champs défilent, verts. Après le tunnel, il y a la lumière ? Oui. On la regarde, assises. La colline se rapproche. Un trou noir s'ouvre. Le tunnel ! Le wagon s'assombrit d'un coup. Le rond jaune devient plus fort. Chouchou serre la main de maman. Tu restes assise ? Oui. Le train fait un bruit creux. Les oreilles de Chouchou chantent un peu. Elle reste sur sa place. C'est long, le noir ? Un peu. On reste assises. Chouchou sent le cacao sur ses doigts. Le rond jaune tremble plus fort. Un bruit d'eau passe sous le train. Tu as entendu l'eau ? Oui. Elle court dessous. Chouchou serre encore la main. Ses pieds restent sur le plancher.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte. Maman dit : on reste assis, avec l'adulte. Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis. Maman dit : maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture. Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La lampe du wagon fait un rond jaune. Le rond tremble un peu sur les genoux. Un carré de chocolat sent le cacao. Le tissu du siège est rêche et bleu. Chouchou vit ici, avec maman. Tu as vu le rond jaune, Chouchou ? Il danse. Oui. Le train va entrer dans un tunnel. En ce moment, Chouchou s'assoit. Maman s'assoit à côté. Le dos de Chouchou touche le dossier. On reste assis, avec l'adulte. D'accord. Le train roule. Les champs défilent, verts. Après le tunnel, il y a la lumière ? Oui. On la regarde, assises. La colline se rapproche. Un trou noir s'ouvre. Le tunnel ! Le wagon s'assombrit d'un coup. Le rond jaune devient plus fort. Chouchou serre la main de maman. Tu restes assise ? Oui. Le train fait un bruit creux. Les oreilles de Chouchou chantent un peu. Elle reste sur sa place. C'est long, le noir ? Un peu. On reste assises. Chouchou sent le cacao sur ses doigts. Le rond jaune tremble plus fort. Un bruit d'eau passe sous le train. Tu as entendu l'eau ? Oui. Elle court dessous. Chouchou serre encore la main. Ses pieds restent sur le plancher.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Pierre et maman montent dans le train. Maman montre la place. Pierre pose ses fesses sur le siège. Il est assis. Son dos est contre le dossier. Ses pieds sont sur le plancher. Ses mains tiennent son doudou. Maman s'assoit à côté. Maman, c'est l'adulte.
+          <t>narrateur|La lampe du wagon fait un rond jaune.
+narrateur|Le rond tremble un peu sur les genoux.
+narrateur|Un carré de chocolat sent le cacao.
+narrateur|Le tissu du siège est rêche et bleu.
+narrateur|Chouchou vit ici, avec maman.
+maman|Tu as vu le rond jaune, Chouchou ?
+enfant-f|Il danse.
+maman|Oui.
+maman|Le train va entrer dans un tunnel.
+narrateur|En ce moment, Chouchou s'assoit.
+narrateur|Maman s'assoit à côté.
+narrateur|Le dos de Chouchou touche le dossier.
 maman|On reste assis, avec l'adulte.
-narrateur|Le train roule. Les arbres défilent. Pierre reste assis, avec maman. Le train s'arrête. Pierre reste assis.
-maman|Maintenant on se lève. Ils descendent ensemble. Plus tard, ils vont en voiture.
-narrateur|Pierre se souvient. Il pose ses fesses sur le siège. Il est assis, avec l'adulte. Maman attache la ceinture. Les pieds restent sur le tapis. Les mains tiennent le doudou. Même leçon, autre transport. On reste assis, avec l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-f|D'accord.
+narrateur|Le train roule.
+narrateur|Les champs défilent, verts.
+enfant-f|Après le tunnel, il y a la lumière ?
+maman|Oui.
+maman|On la regarde, assises.
+narrateur|La colline se rapproche.
+narrateur|Un trou noir s'ouvre.
+enfant-f|Le tunnel !
+narrateur|Le wagon s'assombrit d'un coup.
+narrateur|Le rond jaune devient plus fort.
+narrateur|Chouchou serre la main de maman.
+maman|Tu restes assise ?
+enfant-f|Oui.
+narrateur|Le train fait un bruit creux.
+narrateur|Les oreilles de Chouchou chantent un peu.
+narrateur|Elle reste sur sa place.
+enfant-f|C'est long, le noir ?
+maman|Un peu.
+maman|On reste assises.
+narrateur|Chouchou sent le cacao sur ses doigts.
+narrateur|Le rond jaune tremble plus fort.
+narrateur|Un bruit d'eau passe sous le train.
+maman|Tu as entendu l'eau ?
+enfant-f|Oui.
+enfant-f|Elle court dessous.
+narrateur|Chouchou serre encore la main.
+narrateur|Ses pieds restent sur le plancher.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1391,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Pierre est dans le train. Que fait-il ?</t>
+          <t>Chouchou est dans le train. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Pierre est dans le train. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou est dans le train. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1359,12 +1406,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>assis</t>
+          <t>assise</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>assis | rester assis | avec maman | avec l'adulte</t>
+          <t>assise | rester assise | avec maman | avec l'adulte | assis</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1426,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ses fesses sont sur le siège. Avec qui ?</t>
+          <t>Sa place est sur le siège. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1475,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1551,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Pierre est dans le train. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou est dans le train.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pierre est resté assis. Dans le train, puis dans la voiture. Maman, l'adulte, était à côté.</t>
+          <t>Un trait de jour perce devant. Le trait grandit, tout blanc. La lumière ! Oui. Tu es restée assise. Bravo. Les champs reviennent, plus clairs. Le rond jaune s'affaiblit sur les genoux. Chouchou cligne des yeux. Tu as vu la lumière ? Elle était forte. Maman casse le carré de chocolat. Une moitié pour Chouchou. Il fond. Oui. On le mange, assises. Le cacao sent bon. Le tissu bleu gratte un peu le mollet. Tu veux l'autre moitié ? Après. Je regarde les champs. Un cheval gris lève la tête. Sa crinière part dans le vent. Il court pas. Il nous regarde. Chouchou reste assise. Le chocolat fond encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Pierre est resté &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Dans le train, puis dans la voiture. Maman, l'adulte, était à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un trait de jour perce devant. Le trait grandit, tout blanc. La lumière ! Oui. Tu es restée assise. Bravo. Les champs reviennent, plus clairs. Le rond jaune s'affaiblit sur les genoux. Chouchou cligne des yeux. Tu as vu la lumière ? Elle était forte. Maman casse le carré de chocolat. Une moitié pour Chouchou. Il fond. Oui. On le mange, assises. Le cacao sent bon. Le tissu bleu gratte un peu le mollet. Tu veux l'autre moitié ? Après. Je regarde les champs. Un cheval gris lève la tête. Sa crinière part dans le vent. Il court pas. Il nous regarde. Chouchou reste assise. Le chocolat fond encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,7 +1640,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
@@ -1680,10 +1727,35 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Pierre est resté assis. Dans le train, puis dans la voiture. Maman, l'adulte, était à côté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Un trait de jour perce devant.
+narrateur|Le trait grandit, tout blanc.
+enfant-f|La lumière !
+maman|Oui.
+maman|Tu es restée assise.
+maman|Bravo.
+narrateur|Les champs reviennent, plus clairs.
+narrateur|Le rond jaune s'affaiblit sur les genoux.
+narrateur|Chouchou cligne des yeux.
+maman|Tu as vu la lumière ?
+enfant-f|Elle était forte.
+narrateur|Maman casse le carré de chocolat.
+narrateur|Une moitié pour Chouchou.
+enfant-f|Il fond.
+maman|Oui.
+maman|On le mange, assises.
+narrateur|Le cacao sent bon.
+narrateur|Le tissu bleu gratte un peu le mollet.
+maman|Tu veux l'autre moitié ?
+enfant-f|Après.
+enfant-f|Je regarde les champs.
+narrateur|Un cheval gris lève la tête.
+narrateur|Sa crinière part dans le vent.
+enfant-f|Il court pas.
+maman|Il nous regarde.
+narrateur|Chouchou reste assise.
+narrateur|Le chocolat fond encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête. Pierre donne la main à maman.</t>
+          <t>Le train ralentit près d'un village. Des toits rouges passent. On arrive. On reste assises encore. D'accord. Le train s'arrête. Maintenant on se lève. Elles se lèvent ensemble. Chouchou donne la main à maman. Tu as attendu la lumière, assise. Elle est revenue.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;La voiture s'arrête. Pierre donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train ralentit près d'un village. Des toits rouges passent. On arrive. On reste assises encore. D'accord. Le train s'arrête. Maintenant on se lève. Elles se lèvent ensemble. Chouchou donne la main à maman. Tu as attendu la lumière, assise. Elle est revenue.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,7 +1841,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
@@ -1852,10 +1924,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La voiture s'arrête. Pierre donne la main à maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le train ralentit près d'un village.
+narrateur|Des toits rouges passent.
+maman|On arrive.
+maman|On reste assises encore.
+enfant-f|D'accord.
+narrateur|Le train s'arrête.
+maman|Maintenant on se lève.
+narrateur|Elles se lèvent ensemble.
+narrateur|Chouchou donne la main à maman.
+maman|Tu as attendu la lumière, assise.
+enfant-f|Elle est revenue.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1880,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sur le quai, le jour est large. Mes genoux sont encore chauds. Le rond jaune est resté un peu. Un goût de cacao reste sur la lèvre. Le tunnel est derrière, tout noir et fini.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sur le quai, le jour est large. Mes genoux sont encore chauds. Le rond jaune est resté un peu. Un goût de cacao reste sur la lèvre. Le tunnel est derrière, tout noir et fini.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1941,7 +2022,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2020,10 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sur le quai, le jour est large.
+enfant-f|Mes genoux sont encore chauds.
+maman|Le rond jaune est resté un peu.
+narrateur|Un goût de cacao reste sur la lèvre.
+narrateur|Le tunnel est derrière, tout noir et fini.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2042,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>train puis voiture</t>
+          <t>train de campagne, après-midi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pierre, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
